--- a/Template_Import_POI_PROMIS.xlsx
+++ b/Template_Import_POI_PROMIS.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <r>
       <t xml:space="preserve">Template Bulk Import Data POI — PROMIS v2</t>
@@ -69,19 +69,13 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Sektor</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Pilih dari dropdown (16 sektor baku, sama seperti data existing).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Sub Sektor</t>
-    </r>
+    <t>Kategori</t>
+  </si>
+  <si>
+    <t>Pilih dari dropdown (16 kategori baku, sama seperti data existing).</t>
+  </si>
+  <si>
+    <t>Sub Kategori</t>
   </si>
   <si>
     <r>
@@ -94,19 +88,13 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Area</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">RING 1 s.d. RING 5 kalau ada datanya. Boleh dikosongkan (mayoritas data existing juga kosong di kolom ini).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Outlet</t>
-    </r>
+    <t>Ring Area</t>
+  </si>
+  <si>
+    <t>Ring 1 s.d. Ring 4 kalau ada datanya. Boleh dikosongkan (mayoritas data existing juga kosong di kolom ini).</t>
+  </si>
+  <si>
+    <t>Cabang</t>
   </si>
   <si>
     <r>
@@ -114,9 +102,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Nama kantor penanggung jawab POI. HARUS PERSIS SAMA dengan nama master kantor di sistem (dikonfirmasi terpisah, sama dengan yang dipakai di template user).</t>
-    </r>
+    <t>Nama Cabang penanggung jawab POI. HARUS PERSIS SAMA dengan nama master Cabang di sistem (Kelola Cabang).</t>
   </si>
   <si>
     <r>
@@ -144,6 +130,21 @@
     </r>
   </si>
   <si>
+    <t>Cabang-Cluster</t>
+  </si>
+  <si>
+    <t>Opsional, diabaikan saat import</t>
+  </si>
+  <si>
+    <t>Informasi saja — Area/Cabang-Cluster POI ditentukan dari data Cabang-nya (Kelola Cabang), bukan dari kolom ini.</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Sama seperti Cabang-Cluster di atas — informasi saja, diabaikan saat import.</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Contoh Toko Sinar Jaya (hapus baris ini)</t>
     </r>
@@ -164,7 +165,7 @@
     </r>
   </si>
   <si>
-    <t>Ring 1 (0 - 1 Km)</t>
+    <t>Ring 1</t>
   </si>
   <si>
     <r>
@@ -182,6 +183,9 @@
     </r>
   </si>
   <si>
+    <t>(otomatis dari data Cabang, boleh dikosongkan)</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Food &amp; Beverage</t>
     </r>
@@ -192,7 +196,7 @@
     </r>
   </si>
   <si>
-    <t>Ring 2 (&gt;1 - 3 Km)</t>
+    <t>Ring 2</t>
   </si>
   <si>
     <r>
@@ -205,7 +209,7 @@
     </r>
   </si>
   <si>
-    <t>Ring 3 (&gt;3 - 5 Km)</t>
+    <t>Ring 3</t>
   </si>
   <si>
     <r>
@@ -213,7 +217,7 @@
     </r>
   </si>
   <si>
-    <t>Ring 4 (&gt; 5 Km)</t>
+    <t>Ring 4</t>
   </si>
   <si>
     <r>
@@ -698,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="true" style="0"/>
@@ -795,12 +799,8 @@
       </c>
     </row>
     <row r="8" spans="1:4" customHeight="1" ht="32">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Sektor</t>
-          </r>
-        </is>
+      <c r="B8" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -809,21 +809,13 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Pilih dari dropdown (16 sektor baku, sama seperti data existing).</t>
-          </r>
-        </is>
+      <c r="D8" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4" customHeight="1" ht="32">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Sub Sektor</t>
-          </r>
-        </is>
+      <c r="B9" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -841,12 +833,8 @@
       </c>
     </row>
     <row r="10" spans="1:4" customHeight="1" ht="32">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Area</t>
-          </r>
-        </is>
+      <c r="B10" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -855,21 +843,13 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">RING 1 s.d. RING 5 kalau ada datanya. Boleh dikosongkan (mayoritas data existing juga kosong di kolom ini).</t>
-          </r>
-        </is>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" customHeight="1" ht="32">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Outlet</t>
-          </r>
-        </is>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -878,12 +858,8 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Nama kantor penanggung jawab POI. HARUS PERSIS SAMA dengan nama master kantor di sistem (dikonfirmasi terpisah, sama dengan yang dipakai di template user).</t>
-          </r>
-        </is>
+      <c r="D11" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:4" customHeight="1" ht="32">
@@ -939,6 +915,28 @@
             <t xml:space="preserve">Latitude/Longitude tidak perlu diisi — akan diisi otomatis oleh proses geocoding batch di sistem setelah data masuk.</t>
           </r>
         </is>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="B16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -966,7 +964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="true" style="0"/>
@@ -979,7 +977,7 @@
     <col min="8" max="8" width="18" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="6" t="inlineStr">
         <is>
           <r>
@@ -994,33 +992,17 @@
           </r>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Sektor</t>
-          </r>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Sub Sektor</t>
-          </r>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Area</t>
-          </r>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Outlet</t>
-          </r>
-        </is>
+      <c r="C1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
@@ -1036,8 +1018,14 @@
           </r>
         </is>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <r>
@@ -1067,7 +1055,7 @@
         </is>
       </c>
       <c r="E2" s="7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
@@ -1089,6 +1077,12 @@
             <t xml:space="preserve">Branch Manager</t>
           </r>
         </is>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1143,7 +1137,7 @@
         </is>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -1162,7 +1156,7 @@
         </is>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1181,7 +1175,7 @@
         </is>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1193,7 +1187,7 @@
         </is>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3">
